--- a/Result/checksun_type/海陸空大眾運輸.xlsx
+++ b/Result/checksun_type/海陸空大眾運輸.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>100.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>99.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>99.68</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99.68000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>64031.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>25053.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>25053.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>20848.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25588.72</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25588.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>3744.365424784759</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>64031</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>64031.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.88000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>99.73</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>99.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>36812.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14985.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>14985.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15586.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>32703.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>32703.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>306.0413023357032</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>36812</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36812.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.24000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>8495.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12066.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12066.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>15506.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>38344.86</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>38344.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1700.45891910351</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>8495</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8495.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.08000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>99.54</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>100.03</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>100.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8226.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>14445.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>14445</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17200.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>39987.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>39987.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1472.192845477262</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8226</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8226.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>98.22</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.53</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>100.19</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>100.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7703.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>14823.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>14823.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>17899.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>42324.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>42324.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1064.698710101293</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7703</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7703.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>98.47999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>99.51</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>100.38</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>100.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>13691.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>16643.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>16643</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>18149.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>44241.26</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>44241.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-388.5035627748621</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>13691</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13691.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>99.02</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>100.51</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100.51</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22217.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16186.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>16186.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>18551.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>44965.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>44965.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-50.20679649514568</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22217</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22217.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>99.22</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>100.61</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>100.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>20388.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18946.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18946.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>17549.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>46684.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>46684.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-478.6326019350054</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>20388</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>20388.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>99.19999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>99.39</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>100.71</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>100.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>10119.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>19956.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>19956.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>16534.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>47432.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>47432.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-877.6111596371302</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>10119</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>10119.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>99.34</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>100.76</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>100.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>16800.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20976.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>20976</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>17568.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>49534.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>49534.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-315.9872720816966</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>16800</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>16800.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>99.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>100.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11409.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>19656.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>19656.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>16650.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>53289.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>53289.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-218.2036015710146</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11409</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11409.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>67.1</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>67.84</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>72.96</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.95999999999999</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>98866221.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>74804941.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>74804941.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>71087846.9</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>156284031.04</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>156284031.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-7562941.978300586</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>98866221</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>98866221.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>66.94000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>67.74</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>73.32</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>73.31999999999999</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>45576951.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>64348538.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>64348538.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>67524829.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>159253653.96</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>159253653.96</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-11297280.553215</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>45576951</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>45576951.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>67.1</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>67.82</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>73.72</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>73.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>46955576.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>69288661.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>69288661.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>70829693.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>163706897.24</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>163706897.24</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-10519010.99762076</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>46955576</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>46955576.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>67.24</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>68.01</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>74.14</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>74.14</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>110041406.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>76375781.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>76375781.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>70367222.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>167107903.4</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>167107903.4</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-9179228.203999683</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>110041406</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>110041406.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>67.62</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>68.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>74.57</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>74.56999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>72584552.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>71064478.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>71064478.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>64481932.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>172317692.94</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>172317692.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-13696619.27725531</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>72584552</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>72584552.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>67.85999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>74.95</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>74.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>46584206.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>67370752.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>67370752.59999999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>64236245.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>176130177.44</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>176130177.44</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-15647635.76486138</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>46584206</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>46584206.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>68.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>75.32</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.31999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>70277569.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>70701121.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>70701121.40000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>68292053.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>180396382.82</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>180396382.82</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-15090206.68412498</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>70277569</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>70277569.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>68.4</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>68.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>75.66</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>68.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>75.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>82391176.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>72370724.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>72370724.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>74086195.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>181641583.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>181641583.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-16293518.08006851</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>82391176</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>82391176.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>68.54</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>69.16</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>75.99</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>69.16</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75.98999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>83484888.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>64358663.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>64358663.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>72651412.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>181504609.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>181504609</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-18728509.46427113</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>83484888</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>83484888.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>68.46000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>69.52</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>76.26</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>76.26000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>54115924.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>57899385.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>57899385.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>74829702.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>182258846.32</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>182258846.32</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-21655376.67512232</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>54115924</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>54115924.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>68.56</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>69.91</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>76.56</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>76.56</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>63236050.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>61101738.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>61101738</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>86053205.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>184009067.98</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>184009067.98</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-21916534.52365535</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>63236050</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>63236050.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>23.33</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>24.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>77057770.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>70845370.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>70845370.59999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>93829056.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>129167767.66</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>129167767.66</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-6499332.949721918</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>77057770</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>77057770.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>23.34</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>24.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>56589508.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>69704727.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>69704727</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>92670559.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>130158993.32</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>130158993.32</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-6835691.599824384</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>56589508</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>56589508.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>24.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>24.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>89362570.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>82825684.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>82825684.59999999</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>94646970.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>131181903.56</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>131181903.56</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4879044.042834207</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>89362570</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>89362570.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>23.23</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>23.68</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>24.35</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>71026071.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>105201900.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>105201900.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>95376819.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>132112565.48</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>132112565.48</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-5420981.17417556</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>71026071</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>71026071.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>23.25</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>23.74</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>24.38</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>24.38</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>60190934.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>106186146.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>106186146.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>93131431.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>132556842.6</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>132556842.6</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-4036945.712728366</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>60190934</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>60190934.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>23.24</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>23.78</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>24.41</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>71354552.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>116812741.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>116812741.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>94196953.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>133561542.14</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>133561542.14</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-754668.0280635059</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>71354552</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>71354552.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>23.35</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>122194296.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>115636392.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>115636392.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>99262523.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>134870804.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>134870804.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2765150.593888566</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>122194296</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>122194296.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.52</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>23.94</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>24.48</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>24.48</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>201243649.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>106468256.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>106468256.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>98116548.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>134639948.04</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>134639948.04</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2247592.104038358</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>201243649</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>201243649.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>24.03</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>24.52</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>24.52</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>75947300.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>85551738.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>85551738.59999999</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>91383821.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>132511534.04</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>132511534.04</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-7041621.849463299</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>75947300</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>75947300.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.69</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>24.09</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>24.54</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>24.54</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>113323911.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>80076717.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>80076717.59999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>95286008.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>133454552.88</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>133454552.88</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-6635832.181270555</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>113323911</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>113323911.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>23.78</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>24.57</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>24.57</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>65472807.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>71581166.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>71581166.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>94985374.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>135775448.16</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>135775448.16</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-9823775.541664124</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>65472807</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>65472807.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>27.76</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>52558487.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>100343972.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>100343972.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>98478516.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>92413916.22</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>92413916.22</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-7257776.790309593</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>52558487</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>52558487.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>27.75</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>27.89</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>27.76</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>54319433.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>104350512.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>104350512.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>112357977.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>92646174.84</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>92646174.84</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-2787592.022137582</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>54319433</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>54319433.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>27.77</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>203427957.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>113531512.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>113531512.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>125770873.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>93585432.06</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>93585432.06</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>3509270.290327355</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>203427957</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>203427957.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>27.88</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>27.77</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>133605984.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>96106264.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>96106264.59999999</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>147488599.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>91680188.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>91680188.94</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-3596456.487948716</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>133605984</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>133605984.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>28.08</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>27.79</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>27.79</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>57808002.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>89258099.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>89258099.40000001</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>161049250.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>90198161.82</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>90198161.81999999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-6138124.18948777</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>57808002</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>57808002.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>28.17</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>27.86</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>27.79</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>27.79</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>72591185.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>96613060.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>96613060.40000001</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>165078115.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>89718575.34</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>89718575.34</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-1428646.970633313</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>72591185</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>72591185.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>28.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>27.84</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>27.79</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>27.79</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>100224434.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>120365442.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>120365442</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>165582710.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>88983353.98</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>88983353.98</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>3766288.269538552</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>100224434</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>100224434.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>28.44</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>27.78</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>27.78</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>116301718.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>138010234.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>138010234.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>161068274.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>87631100.58</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>87631100.58</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>8092408.78158626</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>116301718</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>116301718.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>28.49</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>27.75</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>27.77</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>27.77</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>99365158.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>198870934.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>198870934.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>154844032.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>86743979.94</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>86743979.94</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>12261000.19945493</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>99365158</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>99365158.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>28.42</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>27.76</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>94582807.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>232840401.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>232840401.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>153619706.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>85808550.94</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>85808550.94</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>19592869.36071536</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>94582807</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>94582807.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>28.27999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>27.64</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>27.74</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>191353093.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>233543171.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>233543171.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>154416112.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>84833096.6</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>84833096.59999999</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>29879617.57820469</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>191353093</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>191353093.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>33.75</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>536440385.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>636831257.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>636831257.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1058767623.0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>861733292.72</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>861733292.72</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-62384255.55025637</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>536440385</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>536440385.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>33.6</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>36.86</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>419223341.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>736388039.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>736388039</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1078683602.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>915537259.96</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>915537259.96</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-43586060.61003518</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>419223341</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>419223341.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>33.52</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>35.33</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>36.98</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>36.98</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1076709690.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>955731836.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>955731836.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1090992594.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>926992047.58</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>926992047.58</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-2615882.387932301</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1076709690</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1076709690.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>33.59</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>37.1</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>628190408.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>915799938.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>915799938.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1050724929.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>915044455.22</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>915044455.22</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-14438597.94964492</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>628190408</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>628190408.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>33.79</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>35.71</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>37.22</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>37.22</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>523592465.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1080219705.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1080219705.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1029520379.0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>914001607.44</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>914001607.4400001</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>17243109.96039581</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>523592465</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>523592465.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>34.06</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>35.93</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>37.34</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>37.34</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1034224291.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1480703988.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1480703988.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1035666305.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>913910103.94</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>913910103.9400001</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>73093789.79758275</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1034224291</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1034224291.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>34.65</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>36.14</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1515942327.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1420979165.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1420979165.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1008230696.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>907295722.34</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>907295722.34</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>95559430.00079322</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1515942327</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1515942327.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>35.23999999999999</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>36.38</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>37.59</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>37.59</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>877050200.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1226253351.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1226253351.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>936838338.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>886502301.4</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>886502301.4</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>72627718.2196368</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>877050200</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>877050200.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>35.58</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>37.7</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1450289243.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1185649921.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1185649921.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>911094132.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>888919221.9</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>888919221.9</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>105727010.7744266</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1450289243</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1450289243.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>35.9</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>36.77</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>37.79</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>37.79</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2526013880.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>978821052.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>978821052.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>857844524.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>869073140.2</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>869073140.2</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>87817280.86075413</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2526013880</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2526013880.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>36.17</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>37.86</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>735600178.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>590628621.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>590628621.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>689835864.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>832019753.02</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>832019753.02</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-56160590.15380502</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>735600178</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>735600178.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>53.98</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>53.93</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>53.93</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>309731502.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>149304115.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>149304115.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>110162521.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>117855603.56</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>117855603.56</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>16654678.1665608</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>309731502</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>309731502.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>52.7</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>218314058.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>106744330.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>106744330.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>89222972.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>113419591.14</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>113419591.14</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>1495019.715925276</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>218314058</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>218314058.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>48571438.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>72818195.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>72818195.40000001</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>81980229.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>111872773.36</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>111872773.36</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-10420302.63197996</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>48571438</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>48571438.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>51.66</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>53.95</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>87014812.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>72647562.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>72647562.40000001</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>80519028.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>111823206.94</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>111823206.94</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-8883328.749273852</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>87014812</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>87014812.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>82888769.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>74426138.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>74426138.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>77212396.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>110830557.88</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>110830557.88</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-10489322.96150535</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>82888769</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>82888769.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>51.62</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>53.86</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>96932575.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>71020926.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>71020926.40000001</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>72937143.1</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>109856642.7</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>109856642.7</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-11966905.69463946</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>96932575</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>96932575.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>53.89</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>53.89</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>48683383.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>71701614.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>71701614</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>70664021.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>108733892.34</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>108733892.34</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-15155042.18145107</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>48683383</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>48683383.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>54.93</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>47718273.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>91142263.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>91142263</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>73006397.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>108974522.54</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>108974522.54</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-13998715.08470152</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>47718273</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>47718273.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>52.58</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>55.22</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>95907691.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>88390494.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>88390494.59999999</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>76185022.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>108723394.98</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>108723394.98</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-11743460.47917713</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>95907691</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>95907691.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>53.06</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>55.56</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>53.91</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>53.91</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>65862710.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>79998654.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>79998654.40000001</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>103628419.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>108329575.64</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>108329575.64</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-13265410.81131452</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>65862710</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>65862710.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>53.67999999999999</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>55.84</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>53.96</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>53.96</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>100336013.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>74853359.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>74853359.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>154411688.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>108348566.82</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>108348566.82</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-11746755.79253529</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>100336013</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>100336013.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>19.17</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>20.25</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>361997859.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>471089682.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>471089682.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>478098298.8</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>374254724.54</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>374254724.54</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>3471254.677873433</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>361997859</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>361997859.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>20.28</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>288231021.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>501328991.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>501328991</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>471575357.4</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>380868394.02</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>380868394.02</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>13326853.93812042</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>288231021</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>288231021.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>19.06</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>629090477.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>555342721.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>555342721.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>481930880.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>379427409.48</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>379427409.48</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>34833912.16925472</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>629090477</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>629090477.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>19.09</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>20.39</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>558075078.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>534883977.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>534883977.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>462802558.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>371263546.5</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>371263546.5</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>27793556.77911603</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>558075078</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>558075078.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>19.17</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>20.44</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>20.44</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>518053977.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>508674618.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>508674618</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>436732133.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>366738694.22</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>366738694.22</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>24352071.94394946</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>518053977</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>518053977.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>19.26</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>19.88</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>20.49</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>513194402.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>485106915.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>485106915.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>414793544.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>361064605.6</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>361064605.6</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>22853923.2885704</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>513194402</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>513194402.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>19.41</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>20.54</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>558299675.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>441821723.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>441821723.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>412321706.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>360670490.88</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>360670490.88</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>20418168.12772286</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>558299675</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>558299675.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>19.55</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>20.07</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>20.6</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>526796756.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>408519039.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>408519039.2</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>412828855.7</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>352886574.54</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>352886574.54</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>11376589.78623629</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>526796756</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>526796756.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>19.65</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>20.64</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>427028280.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>390721139.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>390721139.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>393353218.7</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>349664803.08</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>349664803.08</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>1429055.270318508</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>427028280</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>427028280.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>19.72</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>20.23</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>20.68</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>20.68</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>400215463.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>364789649.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>364789649.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>389096958.1</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>344148478.86</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>344148478.86</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-2143266.440646887</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>400215463</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>400215463.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>19.78</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>20.27</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>20.71</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>20.71</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>296768445.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>344480173.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>344480173.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>392985438.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>342139673.38</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>342139673.38</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-4297236.119145751</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>296768445</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>296768445.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>58.14</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>57.65</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>50.76</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>50.76</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>56864083.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>49667804.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>49667804.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>55100193.4</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>65077891.96</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>65077891.96</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-1281965.690591685</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>56864083</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>56864083.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>57.72000000000001</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>50.25</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>50.25</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>34267315.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>50744106.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>50744106.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>54082868.7</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>64807510.26</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>64807510.26</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1866398.578095213</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>34267315</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>34267315.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>57.32000000000001</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>57.58</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>49.75</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>57923106.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>66727550.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>66727550.4</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>54074047.8</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>65417577.8</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>65417577.8</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-213563.3253111318</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>57923106</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>57923106.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>49.27</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>49.27</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>53259597.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>64935816.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>64935816.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>53469700.0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>65166202.68</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>65166202.68</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-379291.8811441883</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>53259597</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>53259597.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>57.51</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>48.8</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>46024921.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>62159314.6</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>62159314.6</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>50977637.5</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>65142686.74</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>65142686.74</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-102839.1437219754</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>46024921</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>46024921.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>57.45</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>48.34</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>48.34</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>62245593.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>60532582.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>60532582.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>52060465.0</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>65076480.76</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>65076480.76</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>1070910.022014104</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>62245593</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>62245593.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>57.42</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>47.88</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>114184535.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>57421631.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>57421631</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>51090635.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>65160318.42</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>65160318.42</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>971518.6151365787</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>114184535</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>114184535.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>57.02</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>47.45</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>47.45</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>48964435.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>41420545.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>41420545.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>44543610.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>65562718.96</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>65562718.96</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-4770052.845229052</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>48964435</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>48964435.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>47.01</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>39377089.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>42003583.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>42003583.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>42069892.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>66086974.4</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>66086974.4</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-5814070.901278906</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>39377089</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>39377089.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>46.57</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>46.57</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>37891260.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>39795960.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>39795960.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>44332954.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>66156768.56</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>66156768.56</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-6070664.23487588</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>37891260</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>37891260.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>57.73999999999999</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>46.14</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>46.14</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>46690836.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>43588347.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>43588347.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>51191973.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>66777211.68</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>66777211.68</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-6061220.738768853</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>46690836</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>46690836.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
